--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6224"/>
+  <dimension ref="A1:E6231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106189,6 +106189,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6225" spans="1:5">
+      <c r="A6225" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B6225">
+        <v>890</v>
+      </c>
+      <c r="C6225">
+        <v>0</v>
+      </c>
+      <c r="D6225">
+        <v>0</v>
+      </c>
+      <c r="E6225">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6226" spans="1:5">
+      <c r="A6226" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B6226">
+        <v>890</v>
+      </c>
+      <c r="C6226">
+        <v>0</v>
+      </c>
+      <c r="D6226">
+        <v>0</v>
+      </c>
+      <c r="E6226">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6227" spans="1:5">
+      <c r="A6227" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B6227">
+        <v>890</v>
+      </c>
+      <c r="C6227">
+        <v>0</v>
+      </c>
+      <c r="D6227">
+        <v>0</v>
+      </c>
+      <c r="E6227">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6228" spans="1:5">
+      <c r="A6228" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B6228">
+        <v>890</v>
+      </c>
+      <c r="C6228">
+        <v>0</v>
+      </c>
+      <c r="D6228">
+        <v>0</v>
+      </c>
+      <c r="E6228">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6229" spans="1:5">
+      <c r="A6229" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B6229">
+        <v>890</v>
+      </c>
+      <c r="C6229">
+        <v>0</v>
+      </c>
+      <c r="D6229">
+        <v>0</v>
+      </c>
+      <c r="E6229">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6230" spans="1:5">
+      <c r="A6230" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B6230">
+        <v>890</v>
+      </c>
+      <c r="C6230">
+        <v>0</v>
+      </c>
+      <c r="D6230">
+        <v>0</v>
+      </c>
+      <c r="E6230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6231" spans="1:5">
+      <c r="A6231" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B6231">
+        <v>890</v>
+      </c>
+      <c r="C6231">
+        <v>0</v>
+      </c>
+      <c r="D6231">
+        <v>0</v>
+      </c>
+      <c r="E6231">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6231"/>
+  <dimension ref="A1:E6238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106308,6 +106308,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6232" spans="1:5">
+      <c r="A6232" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B6232">
+        <v>891</v>
+      </c>
+      <c r="C6232">
+        <v>0</v>
+      </c>
+      <c r="D6232">
+        <v>0</v>
+      </c>
+      <c r="E6232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6233" spans="1:5">
+      <c r="A6233" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B6233">
+        <v>891</v>
+      </c>
+      <c r="C6233">
+        <v>0</v>
+      </c>
+      <c r="D6233">
+        <v>0</v>
+      </c>
+      <c r="E6233">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6234" spans="1:5">
+      <c r="A6234" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B6234">
+        <v>891</v>
+      </c>
+      <c r="C6234">
+        <v>0</v>
+      </c>
+      <c r="D6234">
+        <v>0</v>
+      </c>
+      <c r="E6234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6235" spans="1:5">
+      <c r="A6235" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B6235">
+        <v>891</v>
+      </c>
+      <c r="C6235">
+        <v>0</v>
+      </c>
+      <c r="D6235">
+        <v>0</v>
+      </c>
+      <c r="E6235">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6236" spans="1:5">
+      <c r="A6236" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B6236">
+        <v>891</v>
+      </c>
+      <c r="C6236">
+        <v>0</v>
+      </c>
+      <c r="D6236">
+        <v>0</v>
+      </c>
+      <c r="E6236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6237" spans="1:5">
+      <c r="A6237" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B6237">
+        <v>891</v>
+      </c>
+      <c r="C6237">
+        <v>0</v>
+      </c>
+      <c r="D6237">
+        <v>0</v>
+      </c>
+      <c r="E6237">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6238" spans="1:5">
+      <c r="A6238" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B6238">
+        <v>891</v>
+      </c>
+      <c r="C6238">
+        <v>0</v>
+      </c>
+      <c r="D6238">
+        <v>0</v>
+      </c>
+      <c r="E6238">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6238"/>
+  <dimension ref="A1:E6245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106427,6 +106427,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6239" spans="1:5">
+      <c r="A6239" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6239">
+        <v>892</v>
+      </c>
+      <c r="C6239">
+        <v>0</v>
+      </c>
+      <c r="D6239">
+        <v>0</v>
+      </c>
+      <c r="E6239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6240" spans="1:5">
+      <c r="A6240" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6240">
+        <v>892</v>
+      </c>
+      <c r="C6240">
+        <v>0</v>
+      </c>
+      <c r="D6240">
+        <v>0</v>
+      </c>
+      <c r="E6240">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6241" spans="1:5">
+      <c r="A6241" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6241">
+        <v>892</v>
+      </c>
+      <c r="C6241">
+        <v>0</v>
+      </c>
+      <c r="D6241">
+        <v>0</v>
+      </c>
+      <c r="E6241">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6242" spans="1:5">
+      <c r="A6242" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6242">
+        <v>892</v>
+      </c>
+      <c r="C6242">
+        <v>0</v>
+      </c>
+      <c r="D6242">
+        <v>0</v>
+      </c>
+      <c r="E6242">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6243" spans="1:5">
+      <c r="A6243" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6243">
+        <v>892</v>
+      </c>
+      <c r="C6243">
+        <v>0</v>
+      </c>
+      <c r="D6243">
+        <v>0</v>
+      </c>
+      <c r="E6243">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6244" spans="1:5">
+      <c r="A6244" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6244">
+        <v>892</v>
+      </c>
+      <c r="C6244">
+        <v>0</v>
+      </c>
+      <c r="D6244">
+        <v>0</v>
+      </c>
+      <c r="E6244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6245" spans="1:5">
+      <c r="A6245" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B6245">
+        <v>892</v>
+      </c>
+      <c r="C6245">
+        <v>0</v>
+      </c>
+      <c r="D6245">
+        <v>0</v>
+      </c>
+      <c r="E6245">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6245"/>
+  <dimension ref="A1:E6252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106546,6 +106546,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6246" spans="1:5">
+      <c r="A6246" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B6246">
+        <v>893</v>
+      </c>
+      <c r="C6246">
+        <v>0</v>
+      </c>
+      <c r="D6246">
+        <v>0</v>
+      </c>
+      <c r="E6246">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6247" spans="1:5">
+      <c r="A6247" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B6247">
+        <v>893</v>
+      </c>
+      <c r="C6247">
+        <v>0</v>
+      </c>
+      <c r="D6247">
+        <v>0</v>
+      </c>
+      <c r="E6247">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6248" spans="1:5">
+      <c r="A6248" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B6248">
+        <v>893</v>
+      </c>
+      <c r="C6248">
+        <v>0</v>
+      </c>
+      <c r="D6248">
+        <v>0</v>
+      </c>
+      <c r="E6248">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6249" spans="1:5">
+      <c r="A6249" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B6249">
+        <v>893</v>
+      </c>
+      <c r="C6249">
+        <v>0</v>
+      </c>
+      <c r="D6249">
+        <v>0</v>
+      </c>
+      <c r="E6249">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6250" spans="1:5">
+      <c r="A6250" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B6250">
+        <v>893</v>
+      </c>
+      <c r="C6250">
+        <v>0</v>
+      </c>
+      <c r="D6250">
+        <v>0</v>
+      </c>
+      <c r="E6250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6251" spans="1:5">
+      <c r="A6251" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B6251">
+        <v>893</v>
+      </c>
+      <c r="C6251">
+        <v>0</v>
+      </c>
+      <c r="D6251">
+        <v>0</v>
+      </c>
+      <c r="E6251">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6252" spans="1:5">
+      <c r="A6252" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B6252">
+        <v>893</v>
+      </c>
+      <c r="C6252">
+        <v>0</v>
+      </c>
+      <c r="D6252">
+        <v>0</v>
+      </c>
+      <c r="E6252">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6252"/>
+  <dimension ref="A1:E6259"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106665,6 +106665,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6253" spans="1:5">
+      <c r="A6253" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B6253">
+        <v>894</v>
+      </c>
+      <c r="C6253">
+        <v>0</v>
+      </c>
+      <c r="D6253">
+        <v>0</v>
+      </c>
+      <c r="E6253">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6254" spans="1:5">
+      <c r="A6254" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B6254">
+        <v>894</v>
+      </c>
+      <c r="C6254">
+        <v>0</v>
+      </c>
+      <c r="D6254">
+        <v>0</v>
+      </c>
+      <c r="E6254">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6255" spans="1:5">
+      <c r="A6255" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B6255">
+        <v>894</v>
+      </c>
+      <c r="C6255">
+        <v>0</v>
+      </c>
+      <c r="D6255">
+        <v>0</v>
+      </c>
+      <c r="E6255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6256" spans="1:5">
+      <c r="A6256" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B6256">
+        <v>894</v>
+      </c>
+      <c r="C6256">
+        <v>0</v>
+      </c>
+      <c r="D6256">
+        <v>0</v>
+      </c>
+      <c r="E6256">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6257" spans="1:5">
+      <c r="A6257" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B6257">
+        <v>894</v>
+      </c>
+      <c r="C6257">
+        <v>0</v>
+      </c>
+      <c r="D6257">
+        <v>0</v>
+      </c>
+      <c r="E6257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6258" spans="1:5">
+      <c r="A6258" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B6258">
+        <v>894</v>
+      </c>
+      <c r="C6258">
+        <v>0</v>
+      </c>
+      <c r="D6258">
+        <v>0</v>
+      </c>
+      <c r="E6258">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6259" spans="1:5">
+      <c r="A6259" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B6259">
+        <v>894</v>
+      </c>
+      <c r="C6259">
+        <v>0</v>
+      </c>
+      <c r="D6259">
+        <v>0</v>
+      </c>
+      <c r="E6259">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6259"/>
+  <dimension ref="A1:E6266"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106784,6 +106784,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6260" spans="1:5">
+      <c r="A6260" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6260">
+        <v>895</v>
+      </c>
+      <c r="C6260">
+        <v>0</v>
+      </c>
+      <c r="D6260">
+        <v>0</v>
+      </c>
+      <c r="E6260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6261" spans="1:5">
+      <c r="A6261" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6261">
+        <v>895</v>
+      </c>
+      <c r="C6261">
+        <v>0</v>
+      </c>
+      <c r="D6261">
+        <v>0</v>
+      </c>
+      <c r="E6261">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6262" spans="1:5">
+      <c r="A6262" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6262">
+        <v>895</v>
+      </c>
+      <c r="C6262">
+        <v>0</v>
+      </c>
+      <c r="D6262">
+        <v>0</v>
+      </c>
+      <c r="E6262">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6263" spans="1:5">
+      <c r="A6263" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6263">
+        <v>895</v>
+      </c>
+      <c r="C6263">
+        <v>0</v>
+      </c>
+      <c r="D6263">
+        <v>0</v>
+      </c>
+      <c r="E6263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6264" spans="1:5">
+      <c r="A6264" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6264">
+        <v>895</v>
+      </c>
+      <c r="C6264">
+        <v>0</v>
+      </c>
+      <c r="D6264">
+        <v>0</v>
+      </c>
+      <c r="E6264">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6265" spans="1:5">
+      <c r="A6265" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6265">
+        <v>895</v>
+      </c>
+      <c r="C6265">
+        <v>0</v>
+      </c>
+      <c r="D6265">
+        <v>0</v>
+      </c>
+      <c r="E6265">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6266" spans="1:5">
+      <c r="A6266" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6266">
+        <v>895</v>
+      </c>
+      <c r="C6266">
+        <v>0</v>
+      </c>
+      <c r="D6266">
+        <v>0</v>
+      </c>
+      <c r="E6266">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6266"/>
+  <dimension ref="A1:E6273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106903,6 +106903,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6267" spans="1:5">
+      <c r="A6267" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B6267">
+        <v>896</v>
+      </c>
+      <c r="C6267">
+        <v>0</v>
+      </c>
+      <c r="D6267">
+        <v>0</v>
+      </c>
+      <c r="E6267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6268" spans="1:5">
+      <c r="A6268" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B6268">
+        <v>896</v>
+      </c>
+      <c r="C6268">
+        <v>0</v>
+      </c>
+      <c r="D6268">
+        <v>0</v>
+      </c>
+      <c r="E6268">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6269" spans="1:5">
+      <c r="A6269" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B6269">
+        <v>896</v>
+      </c>
+      <c r="C6269">
+        <v>0</v>
+      </c>
+      <c r="D6269">
+        <v>0</v>
+      </c>
+      <c r="E6269">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6270" spans="1:5">
+      <c r="A6270" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B6270">
+        <v>896</v>
+      </c>
+      <c r="C6270">
+        <v>0</v>
+      </c>
+      <c r="D6270">
+        <v>0</v>
+      </c>
+      <c r="E6270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6271" spans="1:5">
+      <c r="A6271" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B6271">
+        <v>896</v>
+      </c>
+      <c r="C6271">
+        <v>0</v>
+      </c>
+      <c r="D6271">
+        <v>0</v>
+      </c>
+      <c r="E6271">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6272" spans="1:5">
+      <c r="A6272" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B6272">
+        <v>896</v>
+      </c>
+      <c r="C6272">
+        <v>0</v>
+      </c>
+      <c r="D6272">
+        <v>0</v>
+      </c>
+      <c r="E6272">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6273" spans="1:5">
+      <c r="A6273" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B6273">
+        <v>896</v>
+      </c>
+      <c r="C6273">
+        <v>0</v>
+      </c>
+      <c r="D6273">
+        <v>0</v>
+      </c>
+      <c r="E6273">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6273"/>
+  <dimension ref="A1:E6280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107022,6 +107022,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6274" spans="1:5">
+      <c r="A6274" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B6274">
+        <v>897</v>
+      </c>
+      <c r="C6274">
+        <v>0</v>
+      </c>
+      <c r="D6274">
+        <v>0</v>
+      </c>
+      <c r="E6274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6275" spans="1:5">
+      <c r="A6275" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B6275">
+        <v>897</v>
+      </c>
+      <c r="C6275">
+        <v>0</v>
+      </c>
+      <c r="D6275">
+        <v>0</v>
+      </c>
+      <c r="E6275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6276" spans="1:5">
+      <c r="A6276" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B6276">
+        <v>897</v>
+      </c>
+      <c r="C6276">
+        <v>0</v>
+      </c>
+      <c r="D6276">
+        <v>0</v>
+      </c>
+      <c r="E6276">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6277" spans="1:5">
+      <c r="A6277" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B6277">
+        <v>897</v>
+      </c>
+      <c r="C6277">
+        <v>0</v>
+      </c>
+      <c r="D6277">
+        <v>0</v>
+      </c>
+      <c r="E6277">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6278" spans="1:5">
+      <c r="A6278" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B6278">
+        <v>897</v>
+      </c>
+      <c r="C6278">
+        <v>0</v>
+      </c>
+      <c r="D6278">
+        <v>0</v>
+      </c>
+      <c r="E6278">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6279" spans="1:5">
+      <c r="A6279" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B6279">
+        <v>897</v>
+      </c>
+      <c r="C6279">
+        <v>0</v>
+      </c>
+      <c r="D6279">
+        <v>0</v>
+      </c>
+      <c r="E6279">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6280" spans="1:5">
+      <c r="A6280" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B6280">
+        <v>897</v>
+      </c>
+      <c r="C6280">
+        <v>0</v>
+      </c>
+      <c r="D6280">
+        <v>0</v>
+      </c>
+      <c r="E6280">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6280"/>
+  <dimension ref="A1:E6287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107141,6 +107141,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6281" spans="1:5">
+      <c r="A6281" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B6281">
+        <v>898</v>
+      </c>
+      <c r="C6281">
+        <v>0</v>
+      </c>
+      <c r="D6281">
+        <v>0</v>
+      </c>
+      <c r="E6281">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6282" spans="1:5">
+      <c r="A6282" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B6282">
+        <v>898</v>
+      </c>
+      <c r="C6282">
+        <v>0</v>
+      </c>
+      <c r="D6282">
+        <v>0</v>
+      </c>
+      <c r="E6282">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6283" spans="1:5">
+      <c r="A6283" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B6283">
+        <v>898</v>
+      </c>
+      <c r="C6283">
+        <v>0</v>
+      </c>
+      <c r="D6283">
+        <v>0</v>
+      </c>
+      <c r="E6283">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6284" spans="1:5">
+      <c r="A6284" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B6284">
+        <v>898</v>
+      </c>
+      <c r="C6284">
+        <v>0</v>
+      </c>
+      <c r="D6284">
+        <v>0</v>
+      </c>
+      <c r="E6284">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6285" spans="1:5">
+      <c r="A6285" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B6285">
+        <v>898</v>
+      </c>
+      <c r="C6285">
+        <v>0</v>
+      </c>
+      <c r="D6285">
+        <v>0</v>
+      </c>
+      <c r="E6285">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6286" spans="1:5">
+      <c r="A6286" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B6286">
+        <v>898</v>
+      </c>
+      <c r="C6286">
+        <v>0</v>
+      </c>
+      <c r="D6286">
+        <v>0</v>
+      </c>
+      <c r="E6286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6287" spans="1:5">
+      <c r="A6287" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B6287">
+        <v>898</v>
+      </c>
+      <c r="C6287">
+        <v>0</v>
+      </c>
+      <c r="D6287">
+        <v>0</v>
+      </c>
+      <c r="E6287">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6287"/>
+  <dimension ref="A1:E6294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107260,6 +107260,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6288" spans="1:5">
+      <c r="A6288" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B6288">
+        <v>899</v>
+      </c>
+      <c r="C6288">
+        <v>0</v>
+      </c>
+      <c r="D6288">
+        <v>0</v>
+      </c>
+      <c r="E6288">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6289" spans="1:5">
+      <c r="A6289" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B6289">
+        <v>899</v>
+      </c>
+      <c r="C6289">
+        <v>0</v>
+      </c>
+      <c r="D6289">
+        <v>0</v>
+      </c>
+      <c r="E6289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6290" spans="1:5">
+      <c r="A6290" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B6290">
+        <v>899</v>
+      </c>
+      <c r="C6290">
+        <v>0</v>
+      </c>
+      <c r="D6290">
+        <v>0</v>
+      </c>
+      <c r="E6290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6291" spans="1:5">
+      <c r="A6291" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B6291">
+        <v>899</v>
+      </c>
+      <c r="C6291">
+        <v>0</v>
+      </c>
+      <c r="D6291">
+        <v>0</v>
+      </c>
+      <c r="E6291">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6292" spans="1:5">
+      <c r="A6292" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B6292">
+        <v>899</v>
+      </c>
+      <c r="C6292">
+        <v>0</v>
+      </c>
+      <c r="D6292">
+        <v>0</v>
+      </c>
+      <c r="E6292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6293" spans="1:5">
+      <c r="A6293" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B6293">
+        <v>899</v>
+      </c>
+      <c r="C6293">
+        <v>0</v>
+      </c>
+      <c r="D6293">
+        <v>0</v>
+      </c>
+      <c r="E6293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6294" spans="1:5">
+      <c r="A6294" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B6294">
+        <v>899</v>
+      </c>
+      <c r="C6294">
+        <v>0</v>
+      </c>
+      <c r="D6294">
+        <v>0</v>
+      </c>
+      <c r="E6294">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6294"/>
+  <dimension ref="A1:E6301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107379,6 +107379,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6295" spans="1:5">
+      <c r="A6295" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B6295">
+        <v>900</v>
+      </c>
+      <c r="C6295">
+        <v>0</v>
+      </c>
+      <c r="D6295">
+        <v>0</v>
+      </c>
+      <c r="E6295">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6296" spans="1:5">
+      <c r="A6296" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B6296">
+        <v>900</v>
+      </c>
+      <c r="C6296">
+        <v>0</v>
+      </c>
+      <c r="D6296">
+        <v>0</v>
+      </c>
+      <c r="E6296">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6297" spans="1:5">
+      <c r="A6297" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B6297">
+        <v>900</v>
+      </c>
+      <c r="C6297">
+        <v>0</v>
+      </c>
+      <c r="D6297">
+        <v>0</v>
+      </c>
+      <c r="E6297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6298" spans="1:5">
+      <c r="A6298" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B6298">
+        <v>900</v>
+      </c>
+      <c r="C6298">
+        <v>0</v>
+      </c>
+      <c r="D6298">
+        <v>0</v>
+      </c>
+      <c r="E6298">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6299" spans="1:5">
+      <c r="A6299" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B6299">
+        <v>900</v>
+      </c>
+      <c r="C6299">
+        <v>0</v>
+      </c>
+      <c r="D6299">
+        <v>0</v>
+      </c>
+      <c r="E6299">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6300" spans="1:5">
+      <c r="A6300" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B6300">
+        <v>900</v>
+      </c>
+      <c r="C6300">
+        <v>0</v>
+      </c>
+      <c r="D6300">
+        <v>0</v>
+      </c>
+      <c r="E6300">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6301" spans="1:5">
+      <c r="A6301" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B6301">
+        <v>900</v>
+      </c>
+      <c r="C6301">
+        <v>0</v>
+      </c>
+      <c r="D6301">
+        <v>0</v>
+      </c>
+      <c r="E6301">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6301"/>
+  <dimension ref="A1:E6308"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107498,6 +107498,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6302" spans="1:5">
+      <c r="A6302" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B6302">
+        <v>901</v>
+      </c>
+      <c r="C6302">
+        <v>0</v>
+      </c>
+      <c r="D6302">
+        <v>0</v>
+      </c>
+      <c r="E6302">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6303" spans="1:5">
+      <c r="A6303" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B6303">
+        <v>901</v>
+      </c>
+      <c r="C6303">
+        <v>0</v>
+      </c>
+      <c r="D6303">
+        <v>0</v>
+      </c>
+      <c r="E6303">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6304" spans="1:5">
+      <c r="A6304" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B6304">
+        <v>901</v>
+      </c>
+      <c r="C6304">
+        <v>0</v>
+      </c>
+      <c r="D6304">
+        <v>0</v>
+      </c>
+      <c r="E6304">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6305" spans="1:5">
+      <c r="A6305" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B6305">
+        <v>901</v>
+      </c>
+      <c r="C6305">
+        <v>0</v>
+      </c>
+      <c r="D6305">
+        <v>0</v>
+      </c>
+      <c r="E6305">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6306" spans="1:5">
+      <c r="A6306" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B6306">
+        <v>901</v>
+      </c>
+      <c r="C6306">
+        <v>0</v>
+      </c>
+      <c r="D6306">
+        <v>0</v>
+      </c>
+      <c r="E6306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6307" spans="1:5">
+      <c r="A6307" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B6307">
+        <v>901</v>
+      </c>
+      <c r="C6307">
+        <v>0</v>
+      </c>
+      <c r="D6307">
+        <v>0</v>
+      </c>
+      <c r="E6307">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6308" spans="1:5">
+      <c r="A6308" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B6308">
+        <v>901</v>
+      </c>
+      <c r="C6308">
+        <v>0</v>
+      </c>
+      <c r="D6308">
+        <v>0</v>
+      </c>
+      <c r="E6308">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6308"/>
+  <dimension ref="A1:E6315"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107617,6 +107617,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6309" spans="1:5">
+      <c r="A6309" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B6309">
+        <v>902</v>
+      </c>
+      <c r="C6309">
+        <v>0</v>
+      </c>
+      <c r="D6309">
+        <v>0</v>
+      </c>
+      <c r="E6309">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6310" spans="1:5">
+      <c r="A6310" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B6310">
+        <v>902</v>
+      </c>
+      <c r="C6310">
+        <v>0</v>
+      </c>
+      <c r="D6310">
+        <v>0</v>
+      </c>
+      <c r="E6310">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6311" spans="1:5">
+      <c r="A6311" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B6311">
+        <v>902</v>
+      </c>
+      <c r="C6311">
+        <v>0</v>
+      </c>
+      <c r="D6311">
+        <v>0</v>
+      </c>
+      <c r="E6311">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6312" spans="1:5">
+      <c r="A6312" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B6312">
+        <v>902</v>
+      </c>
+      <c r="C6312">
+        <v>0</v>
+      </c>
+      <c r="D6312">
+        <v>0</v>
+      </c>
+      <c r="E6312">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6313" spans="1:5">
+      <c r="A6313" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B6313">
+        <v>902</v>
+      </c>
+      <c r="C6313">
+        <v>0</v>
+      </c>
+      <c r="D6313">
+        <v>0</v>
+      </c>
+      <c r="E6313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6314" spans="1:5">
+      <c r="A6314" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B6314">
+        <v>902</v>
+      </c>
+      <c r="C6314">
+        <v>0</v>
+      </c>
+      <c r="D6314">
+        <v>0</v>
+      </c>
+      <c r="E6314">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6315" spans="1:5">
+      <c r="A6315" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B6315">
+        <v>902</v>
+      </c>
+      <c r="C6315">
+        <v>0</v>
+      </c>
+      <c r="D6315">
+        <v>0</v>
+      </c>
+      <c r="E6315">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6315"/>
+  <dimension ref="A1:E6322"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107736,6 +107736,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6316" spans="1:5">
+      <c r="A6316" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B6316">
+        <v>903</v>
+      </c>
+      <c r="C6316">
+        <v>0</v>
+      </c>
+      <c r="D6316">
+        <v>0</v>
+      </c>
+      <c r="E6316">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6317" spans="1:5">
+      <c r="A6317" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B6317">
+        <v>903</v>
+      </c>
+      <c r="C6317">
+        <v>0</v>
+      </c>
+      <c r="D6317">
+        <v>0</v>
+      </c>
+      <c r="E6317">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6318" spans="1:5">
+      <c r="A6318" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B6318">
+        <v>903</v>
+      </c>
+      <c r="C6318">
+        <v>0</v>
+      </c>
+      <c r="D6318">
+        <v>0</v>
+      </c>
+      <c r="E6318">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6319" spans="1:5">
+      <c r="A6319" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B6319">
+        <v>903</v>
+      </c>
+      <c r="C6319">
+        <v>0</v>
+      </c>
+      <c r="D6319">
+        <v>0</v>
+      </c>
+      <c r="E6319">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6320" spans="1:5">
+      <c r="A6320" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B6320">
+        <v>903</v>
+      </c>
+      <c r="C6320">
+        <v>0</v>
+      </c>
+      <c r="D6320">
+        <v>0</v>
+      </c>
+      <c r="E6320">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6321" spans="1:5">
+      <c r="A6321" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B6321">
+        <v>903</v>
+      </c>
+      <c r="C6321">
+        <v>0</v>
+      </c>
+      <c r="D6321">
+        <v>0</v>
+      </c>
+      <c r="E6321">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6322" spans="1:5">
+      <c r="A6322" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B6322">
+        <v>903</v>
+      </c>
+      <c r="C6322">
+        <v>0</v>
+      </c>
+      <c r="D6322">
+        <v>0</v>
+      </c>
+      <c r="E6322">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6322"/>
+  <dimension ref="A1:E6336"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -107855,6 +107855,244 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6323" spans="1:5">
+      <c r="A6323" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B6323">
+        <v>904</v>
+      </c>
+      <c r="C6323">
+        <v>0</v>
+      </c>
+      <c r="D6323">
+        <v>0</v>
+      </c>
+      <c r="E6323">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6324" spans="1:5">
+      <c r="A6324" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B6324">
+        <v>904</v>
+      </c>
+      <c r="C6324">
+        <v>0</v>
+      </c>
+      <c r="D6324">
+        <v>0</v>
+      </c>
+      <c r="E6324">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6325" spans="1:5">
+      <c r="A6325" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B6325">
+        <v>904</v>
+      </c>
+      <c r="C6325">
+        <v>0</v>
+      </c>
+      <c r="D6325">
+        <v>0</v>
+      </c>
+      <c r="E6325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6326" spans="1:5">
+      <c r="A6326" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B6326">
+        <v>904</v>
+      </c>
+      <c r="C6326">
+        <v>0</v>
+      </c>
+      <c r="D6326">
+        <v>0</v>
+      </c>
+      <c r="E6326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6327" spans="1:5">
+      <c r="A6327" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B6327">
+        <v>904</v>
+      </c>
+      <c r="C6327">
+        <v>0</v>
+      </c>
+      <c r="D6327">
+        <v>0</v>
+      </c>
+      <c r="E6327">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6328" spans="1:5">
+      <c r="A6328" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B6328">
+        <v>904</v>
+      </c>
+      <c r="C6328">
+        <v>0</v>
+      </c>
+      <c r="D6328">
+        <v>0</v>
+      </c>
+      <c r="E6328">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6329" spans="1:5">
+      <c r="A6329" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B6329">
+        <v>904</v>
+      </c>
+      <c r="C6329">
+        <v>0</v>
+      </c>
+      <c r="D6329">
+        <v>0</v>
+      </c>
+      <c r="E6329">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6330" spans="1:5">
+      <c r="A6330" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B6330">
+        <v>905</v>
+      </c>
+      <c r="C6330">
+        <v>0</v>
+      </c>
+      <c r="D6330">
+        <v>0</v>
+      </c>
+      <c r="E6330">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6331" spans="1:5">
+      <c r="A6331" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B6331">
+        <v>905</v>
+      </c>
+      <c r="C6331">
+        <v>0</v>
+      </c>
+      <c r="D6331">
+        <v>0</v>
+      </c>
+      <c r="E6331">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6332" spans="1:5">
+      <c r="A6332" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B6332">
+        <v>905</v>
+      </c>
+      <c r="C6332">
+        <v>0</v>
+      </c>
+      <c r="D6332">
+        <v>0</v>
+      </c>
+      <c r="E6332">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6333" spans="1:5">
+      <c r="A6333" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B6333">
+        <v>905</v>
+      </c>
+      <c r="C6333">
+        <v>0</v>
+      </c>
+      <c r="D6333">
+        <v>0</v>
+      </c>
+      <c r="E6333">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6334" spans="1:5">
+      <c r="A6334" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B6334">
+        <v>905</v>
+      </c>
+      <c r="C6334">
+        <v>0</v>
+      </c>
+      <c r="D6334">
+        <v>0</v>
+      </c>
+      <c r="E6334">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6335" spans="1:5">
+      <c r="A6335" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B6335">
+        <v>905</v>
+      </c>
+      <c r="C6335">
+        <v>0</v>
+      </c>
+      <c r="D6335">
+        <v>0</v>
+      </c>
+      <c r="E6335">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6336" spans="1:5">
+      <c r="A6336" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B6336">
+        <v>905</v>
+      </c>
+      <c r="C6336">
+        <v>0</v>
+      </c>
+      <c r="D6336">
+        <v>0</v>
+      </c>
+      <c r="E6336">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6336"/>
+  <dimension ref="A1:E6343"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -108093,6 +108093,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6337" spans="1:5">
+      <c r="A6337" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6337">
+        <v>906</v>
+      </c>
+      <c r="C6337">
+        <v>0</v>
+      </c>
+      <c r="D6337">
+        <v>0</v>
+      </c>
+      <c r="E6337">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6338" spans="1:5">
+      <c r="A6338" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6338">
+        <v>906</v>
+      </c>
+      <c r="C6338">
+        <v>0</v>
+      </c>
+      <c r="D6338">
+        <v>0</v>
+      </c>
+      <c r="E6338">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6339" spans="1:5">
+      <c r="A6339" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6339">
+        <v>906</v>
+      </c>
+      <c r="C6339">
+        <v>0</v>
+      </c>
+      <c r="D6339">
+        <v>0</v>
+      </c>
+      <c r="E6339">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6340" spans="1:5">
+      <c r="A6340" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6340">
+        <v>906</v>
+      </c>
+      <c r="C6340">
+        <v>0</v>
+      </c>
+      <c r="D6340">
+        <v>0</v>
+      </c>
+      <c r="E6340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6341" spans="1:5">
+      <c r="A6341" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6341">
+        <v>906</v>
+      </c>
+      <c r="C6341">
+        <v>0</v>
+      </c>
+      <c r="D6341">
+        <v>0</v>
+      </c>
+      <c r="E6341">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6342" spans="1:5">
+      <c r="A6342" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6342">
+        <v>906</v>
+      </c>
+      <c r="C6342">
+        <v>0</v>
+      </c>
+      <c r="D6342">
+        <v>0</v>
+      </c>
+      <c r="E6342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6343" spans="1:5">
+      <c r="A6343" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B6343">
+        <v>906</v>
+      </c>
+      <c r="C6343">
+        <v>0</v>
+      </c>
+      <c r="D6343">
+        <v>0</v>
+      </c>
+      <c r="E6343">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6343"/>
+  <dimension ref="A1:E6350"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -108212,6 +108212,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6344" spans="1:5">
+      <c r="A6344" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6344">
+        <v>907</v>
+      </c>
+      <c r="C6344">
+        <v>0</v>
+      </c>
+      <c r="D6344">
+        <v>0</v>
+      </c>
+      <c r="E6344">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6345" spans="1:5">
+      <c r="A6345" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6345">
+        <v>907</v>
+      </c>
+      <c r="C6345">
+        <v>0</v>
+      </c>
+      <c r="D6345">
+        <v>0</v>
+      </c>
+      <c r="E6345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6346" spans="1:5">
+      <c r="A6346" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6346">
+        <v>907</v>
+      </c>
+      <c r="C6346">
+        <v>0</v>
+      </c>
+      <c r="D6346">
+        <v>0</v>
+      </c>
+      <c r="E6346">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6347" spans="1:5">
+      <c r="A6347" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6347">
+        <v>907</v>
+      </c>
+      <c r="C6347">
+        <v>0</v>
+      </c>
+      <c r="D6347">
+        <v>0</v>
+      </c>
+      <c r="E6347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6348" spans="1:5">
+      <c r="A6348" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6348">
+        <v>907</v>
+      </c>
+      <c r="C6348">
+        <v>0</v>
+      </c>
+      <c r="D6348">
+        <v>0</v>
+      </c>
+      <c r="E6348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6349" spans="1:5">
+      <c r="A6349" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6349">
+        <v>907</v>
+      </c>
+      <c r="C6349">
+        <v>0</v>
+      </c>
+      <c r="D6349">
+        <v>0</v>
+      </c>
+      <c r="E6349">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6350" spans="1:5">
+      <c r="A6350" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B6350">
+        <v>907</v>
+      </c>
+      <c r="C6350">
+        <v>0</v>
+      </c>
+      <c r="D6350">
+        <v>0</v>
+      </c>
+      <c r="E6350">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6350"/>
+  <dimension ref="A1:E6357"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -108331,6 +108331,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6351" spans="1:5">
+      <c r="A6351" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B6351">
+        <v>908</v>
+      </c>
+      <c r="C6351">
+        <v>0</v>
+      </c>
+      <c r="D6351">
+        <v>0</v>
+      </c>
+      <c r="E6351">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6352" spans="1:5">
+      <c r="A6352" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B6352">
+        <v>908</v>
+      </c>
+      <c r="C6352">
+        <v>0</v>
+      </c>
+      <c r="D6352">
+        <v>0</v>
+      </c>
+      <c r="E6352">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6353" spans="1:5">
+      <c r="A6353" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B6353">
+        <v>908</v>
+      </c>
+      <c r="C6353">
+        <v>0</v>
+      </c>
+      <c r="D6353">
+        <v>0</v>
+      </c>
+      <c r="E6353">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6354" spans="1:5">
+      <c r="A6354" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B6354">
+        <v>908</v>
+      </c>
+      <c r="C6354">
+        <v>0</v>
+      </c>
+      <c r="D6354">
+        <v>0</v>
+      </c>
+      <c r="E6354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6355" spans="1:5">
+      <c r="A6355" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B6355">
+        <v>908</v>
+      </c>
+      <c r="C6355">
+        <v>0</v>
+      </c>
+      <c r="D6355">
+        <v>0</v>
+      </c>
+      <c r="E6355">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6356" spans="1:5">
+      <c r="A6356" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B6356">
+        <v>908</v>
+      </c>
+      <c r="C6356">
+        <v>0</v>
+      </c>
+      <c r="D6356">
+        <v>0</v>
+      </c>
+      <c r="E6356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6357" spans="1:5">
+      <c r="A6357" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B6357">
+        <v>908</v>
+      </c>
+      <c r="C6357">
+        <v>0</v>
+      </c>
+      <c r="D6357">
+        <v>0</v>
+      </c>
+      <c r="E6357">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6357"/>
+  <dimension ref="A1:E6364"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -108450,6 +108450,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6358" spans="1:5">
+      <c r="A6358" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6358">
+        <v>909</v>
+      </c>
+      <c r="C6358">
+        <v>0</v>
+      </c>
+      <c r="D6358">
+        <v>0</v>
+      </c>
+      <c r="E6358">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6359" spans="1:5">
+      <c r="A6359" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6359">
+        <v>909</v>
+      </c>
+      <c r="C6359">
+        <v>0</v>
+      </c>
+      <c r="D6359">
+        <v>0</v>
+      </c>
+      <c r="E6359">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6360" spans="1:5">
+      <c r="A6360" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6360">
+        <v>909</v>
+      </c>
+      <c r="C6360">
+        <v>0</v>
+      </c>
+      <c r="D6360">
+        <v>0</v>
+      </c>
+      <c r="E6360">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6361" spans="1:5">
+      <c r="A6361" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6361">
+        <v>909</v>
+      </c>
+      <c r="C6361">
+        <v>0</v>
+      </c>
+      <c r="D6361">
+        <v>0</v>
+      </c>
+      <c r="E6361">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6362" spans="1:5">
+      <c r="A6362" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6362">
+        <v>909</v>
+      </c>
+      <c r="C6362">
+        <v>0</v>
+      </c>
+      <c r="D6362">
+        <v>0</v>
+      </c>
+      <c r="E6362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6363" spans="1:5">
+      <c r="A6363" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6363">
+        <v>909</v>
+      </c>
+      <c r="C6363">
+        <v>0</v>
+      </c>
+      <c r="D6363">
+        <v>0</v>
+      </c>
+      <c r="E6363">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6364" spans="1:5">
+      <c r="A6364" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B6364">
+        <v>909</v>
+      </c>
+      <c r="C6364">
+        <v>0</v>
+      </c>
+      <c r="D6364">
+        <v>0</v>
+      </c>
+      <c r="E6364">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6364"/>
+  <dimension ref="A1:E6371"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -108569,6 +108569,125 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6365" spans="1:5">
+      <c r="A6365" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B6365">
+        <v>910</v>
+      </c>
+      <c r="C6365">
+        <v>0</v>
+      </c>
+      <c r="D6365">
+        <v>0</v>
+      </c>
+      <c r="E6365">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6366" spans="1:5">
+      <c r="A6366" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B6366">
+        <v>910</v>
+      </c>
+      <c r="C6366">
+        <v>0</v>
+      </c>
+      <c r="D6366">
+        <v>0</v>
+      </c>
+      <c r="E6366">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6367" spans="1:5">
+      <c r="A6367" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B6367">
+        <v>910</v>
+      </c>
+      <c r="C6367">
+        <v>0</v>
+      </c>
+      <c r="D6367">
+        <v>0</v>
+      </c>
+      <c r="E6367">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6368" spans="1:5">
+      <c r="A6368" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B6368">
+        <v>910</v>
+      </c>
+      <c r="C6368">
+        <v>0</v>
+      </c>
+      <c r="D6368">
+        <v>0</v>
+      </c>
+      <c r="E6368">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6369" spans="1:5">
+      <c r="A6369" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B6369">
+        <v>910</v>
+      </c>
+      <c r="C6369">
+        <v>0</v>
+      </c>
+      <c r="D6369">
+        <v>0</v>
+      </c>
+      <c r="E6369">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6370" spans="1:5">
+      <c r="A6370" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B6370">
+        <v>910</v>
+      </c>
+      <c r="C6370">
+        <v>0</v>
+      </c>
+      <c r="D6370">
+        <v>0</v>
+      </c>
+      <c r="E6370">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6371" spans="1:5">
+      <c r="A6371" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B6371">
+        <v>910</v>
+      </c>
+      <c r="C6371">
+        <v>0</v>
+      </c>
+      <c r="D6371">
+        <v>0</v>
+      </c>
+      <c r="E6371">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
